--- a/feedback_forms/016_evaluation_form--feedback_forms.xlsx
+++ b/feedback_forms/016_evaluation_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>intro_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tell us about the product/service</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>feedback_question_1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Is the product/service satisfactory?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select one of the options below</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,33 +579,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feedback_question_2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Are there any features you'd like to see added or improved?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select multiple options below</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>feedback_question_3</t>
+          <t>reported_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>feedback_question_3</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Date of submission</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Format - YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>date_of_submission_reported_date</t>
+          <t>reported_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>date_of_submission.reported_date</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Time of submission</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Format - HH -MM AM/PM</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,43 +650,51 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date_of_submission_reported_datetime</t>
+          <t>feedback_score</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>date_of_submission.reported_datetime</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Feedback score (out of 10)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter a number between 1 and 10</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Additional feedback</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please share any additional thoughts</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,23 +704,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>feedback_question_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Is the product/service easy to use?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select one of the options below</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>feedback_score_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Ease of use score (out of 10)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter a number between 1 and 10</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,253 +758,81 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>feedback_question_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Would you recommend this product/service?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select one of the options below</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>feedback_question_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>How likely are you to recommend this product/service?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Select one of the options below</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>feedback_question_6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What would you like to see improved?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select multiple options below</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>feedback_score</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>feedback_score</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -983,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1050,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes,_add_more_features</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes, add more features</t>
         </is>
       </c>
     </row>
@@ -1067,29 +931,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes,_improve_existing_features</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes, improve existing features</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>feedback_question_3_choices</t>
+          <t>feedback_question_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no_changes_needed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No changes needed</t>
         </is>
       </c>
     </row>
@@ -1101,46 +965,216 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date_of_submission_reported_datetime_choices</t>
+          <t>feedback_question_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date_of_submission_reported_datetime_choices</t>
+          <t>feedback_question_4_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>feedback_question_4_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>feedback_question_5_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>highly_likely</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Highly likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>feedback_question_5_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>somewhat_likely</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Somewhat likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>feedback_question_5_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>not_likely</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Not likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>feedback_question_5_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>not_at_all</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Not at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>feedback_question_6_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>features</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Features</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>feedback_question_6_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>user_interface</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>User interface</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>feedback_question_6_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>performance</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>feedback_question_6_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>feedback_question_6_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
